--- a/artfynd/A 25319-2026 artfynd.xlsx
+++ b/artfynd/A 25319-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134362496</v>
       </c>
       <c r="B2" t="n">
-        <v>92371</v>
+        <v>92378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>134401417</v>
       </c>
       <c r="B4" t="n">
-        <v>92371</v>
+        <v>92378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25319-2026 artfynd.xlsx
+++ b/artfynd/A 25319-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134362496</v>
       </c>
       <c r="B2" t="n">
-        <v>92378</v>
+        <v>92385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,42 +782,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134401403</v>
+        <v>134401417</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>92385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660622</v>
+        <v>660634</v>
       </c>
       <c r="R3" t="n">
-        <v>6557265</v>
+        <v>6557262</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134401417</v>
+        <v>134401403</v>
       </c>
       <c r="B4" t="n">
-        <v>92378</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,26 +903,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>660634</v>
+        <v>660622</v>
       </c>
       <c r="R4" t="n">
-        <v>6557262</v>
+        <v>6557265</v>
       </c>
       <c r="S4" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 25319-2026 artfynd.xlsx
+++ b/artfynd/A 25319-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134362496</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134401417</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,8 +1019,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134401403</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>